--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:43:20Z by SETUP | data 0d9e32e17a42f53c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 77add58a0b581ed9 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="AP7" s="4" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2027-10-01</t>
         </is>
       </c>
       <c r="AQ7" s="4" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AP8" s="4" t="inlineStr">
         <is>
-          <t>2027-05-15</t>
+          <t>2027-10-01</t>
         </is>
       </c>
       <c r="AQ8" s="4" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:43:20Z by SETUP | data 0d9e32e17a42f53c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 77add58a0b581ed9 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>available 2027-04-30, needed 2027-05-15: float 15 d</t>
+          <t>available 2027-04-30, needed 2027-10-01: float 154 d</t>
         </is>
       </c>
     </row>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>available 2027-04-30, needed 2027-05-15: float 15 d</t>
+          <t>available 2027-04-30, needed 2027-10-01: float 154 d</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:43:20Z by SETUP | data 0d9e32e17a42f53c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 77add58a0b581ed9 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 77add58a0b581ed9 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data d8600cf5aed7f9fd | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="5" t="inlineStr">
         <is>
-          <t>Heaviest pieces: GT generator stator 340 t, GT GSU 268 t (transport weights, IEC data).</t>
+          <t>Heaviest pieces (IEC-ALP-REQ-001 section 10): GT core engine 405 t (13.2 x 5.9 x 5.6 m, about 480 t gross on SPMT), GT generator stator 340 t, GT GSU 268 t; landing and haul road designed for 480 t gross SPMT loads.</t>
         </is>
       </c>
       <c r="AT14" s="5" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 77add58a0b581ed9 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data d8600cf5aed7f9fd | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T03:56:53Z by SETUP | data 77add58a0b581ed9 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data d8600cf5aed7f9fd | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data d8600cf5aed7f9fd | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T15:04:39Z by SETUP | data 948253cee8bb8911 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data d8600cf5aed7f9fd | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T15:04:39Z by SETUP | data 948253cee8bb8911 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T04:17:36Z by SETUP | data d8600cf5aed7f9fd | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T15:04:39Z by SETUP | data 948253cee8bb8911 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T15:04:39Z by SETUP | data 948253cee8bb8911 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T17:23:36Z by SETUP | data 5c4c7ac75b502ee5 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T15:04:39Z by SETUP | data 948253cee8bb8911 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T17:23:36Z by SETUP | data 5c4c7ac75b502ee5 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T15:04:39Z by SETUP | data 948253cee8bb8911 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T17:23:36Z by SETUP | data 5c4c7ac75b502ee5 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T17:23:36Z by SETUP | data 5c4c7ac75b502ee5 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T18:13:46Z by SETUP | data b298d4eba195d91d | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T17:23:36Z by SETUP | data 5c4c7ac75b502ee5 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T18:13:46Z by SETUP | data b298d4eba195d91d | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T17:23:36Z by SETUP | data 5c4c7ac75b502ee5 | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T18:13:46Z by SETUP | data b298d4eba195d91d | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T18:13:46Z by SETUP | data b298d4eba195d91d | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T19:01:42Z by EPCE | data c3a98e5f6c62b0fd | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T18:13:46Z by SETUP | data b298d4eba195d91d | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T19:01:42Z by EPCE | data c3a98e5f6c62b0fd | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T18:13:46Z by SETUP | data b298d4eba195d91d | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T19:01:42Z by EPCE | data c3a98e5f6c62b0fd | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T19:01:42Z by EPCE | data c3a98e5f6c62b0fd | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T02:55:46Z by SETUP | data 7f436a85a19a6a8c | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T19:01:42Z by EPCE | data c3a98e5f6c62b0fd | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T02:55:46Z by SETUP | data 7f436a85a19a6a8c | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>max net 665.3 MW (WIN-NG-100) &gt; 640 MW (margin -3.9 %); limited to 640 MW at this point: Export limiter in the plant control system: 640 MW net at the 380 kV revenue meters (TQ-027); line differential 87L main 1 / main 2 with the remote end (plant end by the Contractor, remote end by the Owner), settings coordinated with the TSO (ER-18.02).</t>
+          <t>max net 665.7 MW (WIN-NG-100) &gt; 640 MW (margin -4.0 %); limited to 640 MW at this point: Export limiter in the plant control system: 640 MW net at the 380 kV revenue meters (TQ-027); line differential 87L main 1 / main 2 with the remote end (plant end by the Contractor, remote end by the Owner), settings coordinated with the TSO (ER-18.02).</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-28T19:01:42Z by EPCE | data c3a98e5f6c62b0fd | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T02:55:46Z by SETUP | data 7f436a85a19a6a8c | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T02:55:46Z by SETUP | data 7f436a85a19a6a8c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:04:02Z by SETUP | data 23533dd85dd1747c | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T02:55:46Z by SETUP | data 7f436a85a19a6a8c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:04:02Z by SETUP | data 23533dd85dd1747c | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>streams not mapped to a tie-in (internal to one scope, else an interface is missing): 1 Ambient air to GT compressor inlet; 3 Heated fuel gas to GT combustion system; 4 GT exhaust gas to HRSG inlet; 10 IP superheated steam (joins cold reheat inside the HRSG); 15 IP turbine exhaust (crossover, internal); 16 LP turbine exhaust to condenser (UEEP); 18 Condensate at CEP discharge; 24 IP economiser water to performance fuel gas heater</t>
+          <t>streams not mapped to a tie-in (internal to one scope, else an interface is missing): 1 Ambient air to GT compressor inlet; 3 Heated fuel gas to GT combustion system; 4 GT exhaust gas to HRSG inlet; 10 IP superheated steam (joins cold reheat inside the HRSG); 15 IP turbine exhaust (crossover, internal); 16 LP turbine exhaust to condenser (UEEP); 18 Condensate at CEP discharge; 24 IP economiser water to performance fuel gas heater; 31 Fuel gas to the station preheater burners (water-bath heaters)</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T02:55:46Z by SETUP | data 7f436a85a19a6a8c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:04:02Z by SETUP | data 23533dd85dd1747c | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>

--- a/output/tie_in_register/ALP_tie_in_register.xlsx
+++ b/output/tie_in_register/ALP_tie_in_register.xlsx
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:04:02Z by SETUP | data 23533dd85dd1747c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:51:21Z by EPCE | data 1194a12f026e54a7 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:04:02Z by SETUP | data 23533dd85dd1747c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:51:21Z by EPCE | data 1194a12f026e54a7 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
@@ -16882,7 +16882,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:04:02Z by SETUP | data 23533dd85dd1747c | pressures barg, temperatures degC</t>
+          <t>engine tie_in_register v1.0.0 | generated 2026-09-29T03:51:21Z by EPCE | data 1194a12f026e54a7 | pressures barg, temperatures degC</t>
         </is>
       </c>
     </row>
